--- a/docs/invoice/SOL-2026-0718-001.xlsx
+++ b/docs/invoice/SOL-2026-0718-001.xlsx
@@ -10,7 +10,7 @@
     <sheet name="請求書" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'請求書'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'請求書'!$A$1:$H$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,11 +34,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FF1A1A1A"/>
-      <sz val="22"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="FF555555"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF666666"/>
       <sz val="9"/>
     </font>
     <font>
@@ -50,10 +50,28 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FF1A1A1A"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF1A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1A1A1A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1A1A1A"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="FF1A1A1A"/>
       <sz val="10"/>
     </font>
@@ -62,24 +80,6 @@
       <b val="1"/>
       <color rgb="FF1A1A1A"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FF1A1A1A"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FF1A1A1A"/>
-      <sz val="20"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FF1A1A1A"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -122,21 +122,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8F8F8"/>
+        <fgColor rgb="FFF7F7F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8E8E8"/>
+        <fgColor rgb="FFE2E2E2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -156,79 +156,142 @@
     </border>
     <border>
       <bottom style="hair">
-        <color rgb="FFBBBBBB"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF1A1A1A"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1A1A1A"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1A1A1A"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color rgb="FF1A1A1A"/>
       </right>
       <top style="medium">
         <color rgb="FF1A1A1A"/>
       </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1A1A1A"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color rgb="FF1A1A1A"/>
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1A1A1A"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF1A1A1A"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1A1A1A"/>
+      </bottom>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FF8C8C8C"/>
       </left>
       <right style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FF8C8C8C"/>
       </right>
       <top style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FF8C8C8C"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FF8C8C8C"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FF8C8C8C"/>
       </left>
-    </border>
-    <border>
+      <right/>
+      <top style="thin">
+        <color rgb="FF8C8C8C"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF8C8C8C"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FF8C8C8C"/>
       </right>
       <top style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FF8C8C8C"/>
       </top>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FF8C8C8C"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8C8C8C"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8C8C8C"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FF8C8C8C"/>
       </bottom>
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FF8C8C8C"/>
       </bottom>
     </border>
     <border>
@@ -236,22 +299,24 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FF8C8C8C"/>
       </bottom>
     </border>
     <border>
+      <left/>
       <right style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FF8C8C8C"/>
       </right>
+      <top/>
       <bottom style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FF8C8C8C"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,68 +338,76 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,23 +784,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H41"/>
+  <dimension ref="B2:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="1.6" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="1.6" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1">
+    <row r="1" ht="6" customHeight="1"/>
+    <row r="2" ht="42" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>請 求 書</t>
+          <t>請　求　書</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -737,7 +811,8 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
     </row>
-    <row r="4">
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="16" customHeight="1">
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>請求書番号</t>
@@ -749,7 +824,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
+    <row r="5" ht="28" customHeight="1">
       <c r="B5" s="5" t="inlineStr">
         <is>
           <t>竹内産業株式会社 エネルギー事業部 御中</t>
@@ -769,7 +844,8 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="6" ht="10" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="7" t="inlineStr">
         <is>
           <t>下記のとおりご請求申し上げます。</t>
@@ -781,7 +857,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="17" customHeight="1">
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>事業主</t>
@@ -793,7 +869,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="17" customHeight="1">
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>登録番号</t>
@@ -805,273 +881,367 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="B10" s="9" t="inlineStr">
+    <row r="10" ht="17" customHeight="1">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>所在地</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>連絡先</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>support@local-support.jp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="10" customHeight="1"/>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>ご請求金額</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="11">
-        <f>E22</f>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="12">
+        <f>E28</f>
         <v>8800</v>
       </c>
-      <c r="E10" s="10" t="n"/>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>所在地</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="E13" s="13" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>（消費税込）</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>連絡先</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>support@local-support.jp</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+    </row>
+    <row r="15" ht="10" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>品目</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="B15" s="15" t="inlineStr">
+    <row r="17" ht="52" customHeight="1">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>業者ご紹介手数料
-案件ID：SOL-2026-0718-001／太陽光パネル清掃・除草（兵庫県佐用町）
-成約金額 88,000円（税込）の10%</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
+案件ID：SOL-2026-0718-001
+太陽光パネル清掃・除草（兵庫県佐用町）／成約金額 88,000円（税込）の10%</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>1式</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D17" s="21" t="n">
         <v>8000</v>
       </c>
-      <c r="E15" s="17">
-        <f>D15</f>
+      <c r="E17" s="21">
+        <f>IF(D17="","",D17)</f>
         <v>8000</v>
       </c>
     </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="B17" s="18" t="n"/>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="B18" s="18" t="n"/>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
-      <c r="E18" s="18" t="n"/>
-    </row>
-    <row r="20">
-      <c r="D20" s="19" t="inlineStr">
+    <row r="18" ht="21" customHeight="1">
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="21">
+        <f>IF(D18="","",D18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="B19" s="22" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="21">
+        <f>IF(D19="","",D19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="B20" s="22" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="21">
+        <f>IF(D20="","",D20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="21">
+        <f>IF(D21="","",D21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="21">
+        <f>IF(D22="","",D22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="21">
+        <f>IF(D23="","",D23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="21">
+        <f>IF(D24="","",D24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="8" customHeight="1"/>
+    <row r="26" ht="21" customHeight="1">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>小計（10%対象）</t>
         </is>
       </c>
-      <c r="E20" s="20">
-        <f>SUM(E15:E18)</f>
+      <c r="E26" s="25">
+        <f>SUM(E17:E24)</f>
         <v>8000</v>
       </c>
     </row>
-    <row r="21">
-      <c r="D21" s="19" t="inlineStr">
+    <row r="27" ht="21" customHeight="1">
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>消費税（10%）</t>
         </is>
       </c>
-      <c r="E21" s="20">
-        <f>ROUND(E20*0.1,0)</f>
+      <c r="E27" s="25">
+        <f>ROUND(E26*0.1,0)</f>
         <v>800</v>
       </c>
     </row>
-    <row r="22">
-      <c r="D22" s="21" t="inlineStr">
+    <row r="28" ht="21" customHeight="1">
+      <c r="D28" s="26" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="E22" s="22">
-        <f>E20+E21</f>
+      <c r="E28" s="27">
+        <f>E26+E27</f>
         <v>8800</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="23" t="inlineStr">
+    <row r="29" ht="12" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>お振込先</t>
         </is>
       </c>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="24" t="n"/>
-      <c r="E24" s="25" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="26" t="inlineStr">
-        <is>
-          <t>金融機関</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="n"/>
-      <c r="E25" s="28" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="26" t="inlineStr">
-        <is>
-          <t>種別・番号</t>
-        </is>
-      </c>
-      <c r="C26" s="27" t="n"/>
-      <c r="E26" s="28" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="29" t="inlineStr">
-        <is>
-          <t>口座名義</t>
-        </is>
-      </c>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="32" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="33" t="inlineStr">
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="30" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　金融機関</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="n"/>
+      <c r="D31" s="33" t="n"/>
+      <c r="E31" s="34" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　種別・番号</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33" t="n"/>
+      <c r="E32" s="34" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　口座名義</t>
+        </is>
+      </c>
+      <c r="C33" s="36" t="n"/>
+      <c r="D33" s="37" t="n"/>
+      <c r="E33" s="38" t="n"/>
+    </row>
+    <row r="34" ht="12" customHeight="1"/>
+    <row r="35" ht="20" customHeight="1">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="14" customHeight="1">
-      <c r="B30" s="34" t="inlineStr">
-        <is>
-          <t>・お支払期限：2026年9月30日（8月末締め・翌月末払い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="14" customHeight="1">
-      <c r="B31" s="34" t="inlineStr">
-        <is>
-          <t>・振込手数料は恐れ入りますが貴社にてご負担をお願いいたします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="14" customHeight="1">
-      <c r="B32" s="34" t="inlineStr">
-        <is>
-          <t>・本請求書は適格請求書（インボイス）として発行しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="B33" s="34" t="inlineStr">
-        <is>
-          <t>・「ロカサポ（local-support.jp）」は屋号「ローカル情報局」として藤波が運営しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="14" customHeight="1">
-      <c r="B34" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　日頃のご連絡は運営担当の寺尾より差し上げております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="35" t="inlineStr">
-        <is>
-          <t>【記入方法】</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="36" t="inlineStr">
-        <is>
-          <t>黄色いセルに入力してください（所在地・金融機関・種別と番号・口座名義の4箇所）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="37" t="inlineStr">
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="29" t="n"/>
+      <c r="E35" s="29" t="n"/>
+      <c r="F35" s="29" t="n"/>
+      <c r="G35" s="29" t="n"/>
+      <c r="H35" s="30" t="n"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・お支払期限：2026年9月30日（8月末締め・翌月末払い）</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="33" t="n"/>
+      <c r="G36" s="33" t="n"/>
+      <c r="H36" s="34" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="B37" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・振込手数料は恐れ入りますが貴社にてご負担をお願いいたします。</t>
+        </is>
+      </c>
+      <c r="C37" s="33" t="n"/>
+      <c r="D37" s="33" t="n"/>
+      <c r="E37" s="33" t="n"/>
+      <c r="F37" s="33" t="n"/>
+      <c r="G37" s="33" t="n"/>
+      <c r="H37" s="34" t="n"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="B38" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・本請求書は適格請求書（インボイス）として発行しております。</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+      <c r="G38" s="33" t="n"/>
+      <c r="H38" s="34" t="n"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="B39" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・「ロカサポ（local-support.jp）」は屋号「ローカル情報局」として藤波が運営しております。</t>
+        </is>
+      </c>
+      <c r="C39" s="33" t="n"/>
+      <c r="D39" s="33" t="n"/>
+      <c r="E39" s="33" t="n"/>
+      <c r="F39" s="33" t="n"/>
+      <c r="G39" s="33" t="n"/>
+      <c r="H39" s="34" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="B40" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　日頃のご連絡は運営担当の寺尾より差し上げております。</t>
+        </is>
+      </c>
+      <c r="C40" s="37" t="n"/>
+      <c r="D40" s="37" t="n"/>
+      <c r="E40" s="37" t="n"/>
+      <c r="F40" s="37" t="n"/>
+      <c r="G40" s="37" t="n"/>
+      <c r="H40" s="38" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="41" t="inlineStr">
+        <is>
+          <t>【記入方法 — 印刷範囲の外なのでPDFには出ません】</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="42" t="inlineStr">
+        <is>
+          <t>黄色いセルに入力してください：H10（所在地）／C31（金融機関）／C32（種別・番号）／C33（口座名義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="43" t="inlineStr">
         <is>
           <t>入力例：〒150-0002 東京都渋谷区渋谷1-2-3 ／ ◯◯銀行 △△支店 ／ 普通 1234567 ／ フジナミ ケイスケ</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="36" t="inlineStr">
-        <is>
-          <t>金額を変えるときは単価（D列）だけ直せば、消費税と合計は自動で再計算されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="37" t="inlineStr">
-        <is>
-          <t>この【記入方法】は印刷範囲の外にあるため、PDFには出ません。</t>
+    <row r="46">
+      <c r="B46" s="42" t="inlineStr">
+        <is>
+          <t>金額を変えるときは単価（D17）だけ直せば、金額・小計・消費税・合計・上部の請求金額まで自動で再計算されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="42" t="inlineStr">
+        <is>
+          <t>明細を追加するときは 18〜24 行目の単価（D列）に入力してください。金額欄は自動で入ります。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="B10:C11"/>
+  <mergeCells count="15">
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B13:C14"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B39:H39"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B38:H38"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="D10:E11"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B14"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="D13:E14"/>
   </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>